--- a/astro-site/public/dl/kit-inventario/04-recepcion-mercancias.xlsx
+++ b/astro-site/public/dl/kit-inventario/04-recepcion-mercancias.xlsx
@@ -690,7 +690,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Umbrales tomados del Reglamento (CE) 853/2004 (Anexo III), el RD 3484/2000 y el Reglamento (CE) 589/2008. Documentan tus registros; no sustituyen a tu plan APPCC ni a un asesor.</t>
+          <t>Umbrales tomados del Reglamento (CE) 853/2004 (Anexo III), del Reglamento (CE) 589/2008 y del criterio habitual de los planes APPCC para comidas preparadas (el RD 3484/2000, que los fijaba, fue derogado por el RD 1021/2022). Documentan tus registros; no sustituyen a tu plan APPCC ni a un asesor.</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="E11" s="30" t="inlineStr">
         <is>
-          <t>RD 3484/2000, art. 6</t>
+          <t>Criterio habitual del plan APPCC (el RD 3484/2000, que lo fijaba, fue derogado por el RD 1021/2022)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E12" s="28" t="inlineStr">
         <is>
-          <t>RD 3484/2000, art. 6</t>
+          <t>Criterio habitual del plan APPCC (el RD 3484/2000, que lo fijaba, fue derogado por el RD 1021/2022)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
